--- a/etf_holdings/2026-09-29_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:35</t>
+          <t>2026-09-29 01:00:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:36</t>
+          <t>2026-09-29 01:00:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:37</t>
+          <t>2026-09-29 01:00:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:39</t>
+          <t>2026-09-29 01:00:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:39</t>
+          <t>2026-09-29 01:00:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:39</t>
+          <t>2026-09-29 01:00:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:39</t>
+          <t>2026-09-29 01:00:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:39</t>
+          <t>2026-09-29 01:00:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:41</t>
+          <t>2026-09-29 01:39:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:42</t>
+          <t>2026-09-29 01:39:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:44</t>
+          <t>2026-09-29 01:39:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:45</t>
+          <t>2026-09-29 01:39:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:45</t>
+          <t>2026-09-29 01:39:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:45</t>
+          <t>2026-09-29 01:39:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:45</t>
+          <t>2026-09-29 01:39:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:45</t>
+          <t>2026-09-29 01:39:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,20 +522,20 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.92%3,800,000</t>
+          <t>12.78%4,000,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.92%</t>
+          <t>12.78%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3800000</v>
+        <v>4000000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.64%1,350,000</t>
+          <t>8.57%1,350,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.64%</t>
+          <t>8.57%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.33%503</t>
+          <t>+0.6%506</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.29%13,000,000</t>
+          <t>8.49%13,000,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.29%</t>
+          <t>8.49%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,33 +692,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1185</v>
+        <v>1165</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.66%5,100,000</t>
+          <t>7.82%5,200,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.66%</t>
+          <t>7.82%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5100000</v>
+        <v>5200000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>-1.9%12115</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>12350</v>
+        <v>12115</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,33 +814,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.23%1,080,000</t>
+          <t>7.16%1,130,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.23%</t>
+          <t>7.16%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1080000</v>
+        <v>1130000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3555</v>
+        <v>1270</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.63%1,250,000</t>
+          <t>5.57%3,400,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.57%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1250000</v>
+        <v>3400000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,33 +936,33 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+6.18%962</t>
+          <t>-0.73%955</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+6.18%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.37%4,400,000</t>
+          <t>5.55%4,500,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.55%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4400000</v>
+        <v>4500000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1240</v>
+        <v>3400</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.19%3,300,000</t>
+          <t>5.49%1,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.19%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3300000</v>
+        <v>1250000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,33 +1058,33 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.22%580</t>
+          <t>-5.52%548</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.92%6,700,000</t>
+          <t>4.25%6,000,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.92%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6700000</v>
+        <v>6000000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>-2.22%19395</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>19835</v>
+        <v>19395</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.53%140,500</t>
+          <t>3.52%140,500</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.08%1,150,020</t>
+          <t>3.12%1,150,020</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.75%2700</t>
+          <t>-1.85%2650</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+5.47%810</t>
+          <t>-1.73%796</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+5.47%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:28</t>
+          <t>2026-09-29 22:54:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6920</v>
+        <v>6895</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.54%290,000</t>
+          <t>2.58%290,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>+3.78%247</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1910</v>
+        <v>247</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.11%871,000</t>
+          <t>2.23%7,000,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>871000</v>
+        <v>7000000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,34 +1480,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>154</v>
+        <v>1835</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.03%10,400,000</t>
+          <t>2.06%871,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>10400000</v>
+        <v>871000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+4.62%238</t>
+          <t>-0.32%153.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+4.62%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>238</v>
+        <v>153.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.02%6,700,000</t>
+          <t>2.06%10,400,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6700000</v>
+        <v>10400000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,33 +1668,33 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1895</v>
+        <v>1810</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.78%740,000</t>
+          <t>1.00%430,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>740000</v>
+        <v>430000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,33 +1729,33 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5415</v>
+        <v>5185</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.72%250,000</t>
+          <t>1.00%150,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>-3.6%6020</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6245</v>
+        <v>6020</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.1%5670</t>
+          <t>-1.5%5585</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5670</v>
+        <v>5585</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.88%338.5</t>
+          <t>-0.59%336.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>338.5</v>
+        <v>336.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,21 +1968,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2295</v>
+        <v>2445</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>0%250.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2043,11 +2043,11 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2340</v>
+        <v>250.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,25 +2090,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.15%250.5</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>250.5</v>
+        <v>2185</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0%243</t>
+          <t>-2.06%238</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-4.06%2125</t>
+          <t>-0.47%2115</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2125</v>
+        <v>2115</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:29</t>
+          <t>2026-09-29 22:54:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.5%184.5</t>
+          <t>+0.54%185.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>184.5</v>
+        <v>185.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.45%170.5</t>
+          <t>+4.69%178.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>170.5</v>
+        <v>178.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>-0.67%1485</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.96%150</t>
+          <t>+1%151.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>150</v>
+        <v>151.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.9%110.5</t>
+          <t>+0.9%111.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>110.5</v>
+        <v>111.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.52%953</t>
+          <t>+1.05%963</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>953</v>
+        <v>963</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.58%749</t>
+          <t>+1.47%760</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.57%69.2</t>
+          <t>-0.72%68.7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>69.2</v>
+        <v>68.7</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.58%68.5</t>
+          <t>+0.29%68.7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>68.5</v>
+        <v>68.7</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.92%538</t>
+          <t>-3.16%521</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%45.6</t>
+          <t>-1.54%44.9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>45.6</v>
+        <v>44.9</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.22%45.15</t>
+          <t>-2.77%43.9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>45.15</v>
+        <v>43.9</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.8%49.6</t>
+          <t>-1.01%49.1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.11%45.75</t>
+          <t>-1.86%44.9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>45.75</v>
+        <v>44.9</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.3%311</t>
+          <t>-5.31%294.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>311</v>
+        <v>294.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:30</t>
+          <t>2026-09-29 22:54:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.05%42.5</t>
+          <t>-1.65%41.8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>42.5</v>
+        <v>41.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:32</t>
+          <t>2026-09-29 22:54:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.02%38.95</t>
+          <t>0%38.95</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:32</t>
+          <t>2026-09-29 22:54:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.67%222.5</t>
+          <t>+1.57%226</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>222.5</v>
+        <v>226</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:32</t>
+          <t>2026-09-29 22:54:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.49%207</t>
+          <t>+0.24%207.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>207</v>
+        <v>207.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:32</t>
+          <t>2026-09-29 22:54:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.34%145</t>
+          <t>-0.69%144</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:32</t>
+          <t>2026-09-29 22:54:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.19%74.5</t>
+          <t>-0.81%73.9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>74.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-29_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:37</t>
+          <t>2026-09-29 23:04:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:39</t>
+          <t>2026-09-29 23:04:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:40</t>
+          <t>2026-09-29 23:05:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:41</t>
+          <t>2026-09-29 23:05:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:41</t>
+          <t>2026-09-29 23:05:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:41</t>
+          <t>2026-09-29 23:05:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:41</t>
+          <t>2026-09-29 23:05:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:41</t>
+          <t>2026-09-29 23:05:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:38</t>
+          <t>2026-09-29 23:50:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:49</t>
+          <t>2026-09-29 23:50:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:00</t>
+          <t>2026-09-29 23:50:17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:11</t>
+          <t>2026-09-29 23:50:18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:11</t>
+          <t>2026-09-29 23:50:18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:11</t>
+          <t>2026-09-29 23:50:18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:11</t>
+          <t>2026-09-29 23:50:18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 23:05:11</t>
+          <t>2026-09-29 23:50:18</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
